--- a/excel-files/LAS PINAS/LAS PIÑAS NATIONAL HIGH SCHOOL - ALMANZA.xlsx
+++ b/excel-files/LAS PINAS/LAS PIÑAS NATIONAL HIGH SCHOOL - ALMANZA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="406" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2197BBE7-E770-4015-A782-A8AD12293748}"/>
+  <xr:revisionPtr revIDLastSave="503" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0820AA55-38E6-4471-93F6-D8F59AD10696}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5964,12 +5964,15 @@
     <protectedRange sqref="I1:I98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14:H19 H21:H29 H31:H39 H91:H98 H61:H69 H41:H49 H2:H6 H71:H79 H81:H89 H8:H12 H51:H59" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H91:H98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I14:I19 I21:I29 I31:I39 I41:I49 I91:I98 I61:I69 I71:I79 I81:I89 I2:I6 I8:I12 I51:I59" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H6 H8:H12 H14:H19 H21:H29 H31:H39 H41:H49 H51:H59 H61:H69 H71:H79 H81:H89" xr:uid="{BD36D9BA-0744-4E54-BFF9-8399A7C76880}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6771,7 +6774,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="38.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -8607,7 +8610,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -12705,7 +12708,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="38.25">
       <c r="A103" s="1" t="s">
         <v>27</v>
       </c>
@@ -14450,15 +14453,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 X112:X127 F53:F61 F5:F12 F73:F81 F83:F91 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 F93:F101" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G103:G110 G63:G71 G73:G81 G83:G91 G93:G101" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{2BB66D44-B768-4648-A08E-927581311FCD}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14688,7 +14694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -14757,7 +14763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="19.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14826,7 +14832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14895,7 +14901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14964,7 +14970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -15033,7 +15039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -15102,7 +15108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -15172,7 +15178,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="38.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -16347,7 +16353,7 @@
       </c>
     </row>
     <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -17107,7 +17113,7 @@
       </c>
     </row>
     <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -17383,7 +17389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -18005,7 +18011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="19.5">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -22238,7 +22244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>27</v>
       </c>
@@ -23001,7 +23007,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
+    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113 V2:X10" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -23011,12 +23017,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X67:X77 X103:X113 X91:X101 X79:X89" xr:uid="{0D16A010-F317-4F53-9158-8860F9BD0466}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
